--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_09-09-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_09-09-2025.xlsx
@@ -538,17 +538,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>£10.98</t>
+          <t>£10.95</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>£10.98</t>
+          <t>£10.95</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>£10.98</t>
+          <t>£10.95</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -659,17 +659,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>£12.33</t>
+          <t>£12.30</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>£12.33</t>
+          <t>£12.30</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>£12.33</t>
+          <t>£12.30</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£21.00</t>
+          <t>£20.59</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>£21.00</t>
+          <t>£20.59</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>£21.00</t>
+          <t>£20.59</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1385,17 +1385,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>£26.40</t>
+          <t>£25.79</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>£26.40</t>
+          <t>£25.79</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>£26.40</t>
+          <t>£25.79</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1627,17 +1627,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£28.35</t>
+          <t>£28.00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£28.35</t>
+          <t>£28.00</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£28.35</t>
+          <t>£28.00</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>£28.00</t>
+          <t>Error: 'NoneType' object has no attribute 'find'</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>£27.48</t>
+          <t>£26.87</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1748,17 +1748,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>£36.50</t>
+          <t>£36.30</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>£36.50</t>
+          <t>£36.30</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>£36.50</t>
+          <t>£36.30</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>£34.90</t>
+          <t>£42.00</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1990,17 +1990,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>£42.50</t>
+          <t>£41.09</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>£42.50</t>
+          <t>£41.09</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>£42.50</t>
+          <t>£41.09</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>£43.99</t>
+          <t>£42.00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>£43.99</t>
+          <t>£42.00</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Error: ("Connection broken: InvalidChunkLength(got length b'', 0 bytes read)", InvalidChunkLength(got length b'', 0 bytes read))</t>
+          <t>£42.00</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>£30.00</t>
+          <t>£29.58</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>£55.00</t>
+          <t>£43.63</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>£55.00</t>
+          <t>£43.63</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>£52.00</t>
+          <t>£44.38</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">

--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_09-09-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_09-09-2025.xlsx
@@ -1657,7 +1657,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'find'</t>
+          <t>£28.00</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>£38.00</t>
+          <t>£36.00</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
